--- a/pcbs/lara_hat_v2/hat-bom.xlsx
+++ b/pcbs/lara_hat_v2/hat-bom.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="55">
   <si>
     <t xml:space="preserve">Descr</t>
   </si>
@@ -61,10 +61,10 @@
     <t xml:space="preserve">HC-49</t>
   </si>
   <si>
-    <t xml:space="preserve">Cristal 8 MHZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://es.rs-online.com/web/p/unidades-de-cristal/6938793</t>
+    <t xml:space="preserve">Cristal 12 MHZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://es.rs-online.com/web/p/unidades-de-cristal/6938803</t>
   </si>
   <si>
     <t xml:space="preserve">R10k</t>
@@ -88,6 +88,12 @@
     <t xml:space="preserve">https://es.rs-online.com/web/p/resistencias-de-montaje-en-superficie/1995724</t>
   </si>
   <si>
+    <t xml:space="preserve">R4.7k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://es.rs-online.com/web/p/resistencias-de-montaje-en-superficie/2230528</t>
+  </si>
+  <si>
     <t xml:space="preserve">C22p</t>
   </si>
   <si>
@@ -161,6 +167,24 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.amazon.es/-/en/Briny-River-Connector-Compatible-Raspberry/dp/B0F6V6PCVP?crid=3R49N9ZINWW50&amp;dib=eyJ2IjoiMSJ9.j6t6JSnbQ_Uw-f34Oi7ZAEme0Iu_6gfHHMhiohSGC1dWd5gF2dPv9bNCBIZVb6tZcAsNYQw1nUxdyM9SNI-81fbcvW76_-2uM4sYTvPmZ_tgIuPeXhx34_28PrM6UjkyMkX3-Nc-GnJOawoDA3vCJ4gmYa86nZvKOBNcKvm6dC7Gmk6pF7Cp58tep7_hapmsrfEFeTUEdMZU-jZl_bptBPAIEwaWWnsIUXxELTiSi5BsCVikQegWgJR8gpMmc59giqKOp6yif0wogl4IL1xyUXN7e-AYUI3i7XKJju1zJQU.3eAmLR5O4Bt7WpWH8w9pJ6VA7_JDPCfTRFvv6EzkhKY&amp;dib_tag=se&amp;keywords=raspberry+pi+female+header&amp;qid=1776254357&amp;s=industrial&amp;sprefix=raspberry+pi+female+header%2Cindustrial%2C98&amp;sr=1-4&amp;language=es_ES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D42V55F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12V-5V-Buck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pololu.com/product/5571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULTRAFIT HDR RT 1R BLK NAIL 02 C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conn_Molex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.digikey.es/es/products/detail/molex/1723103102/15709357</t>
   </si>
 </sst>
 </file>
@@ -175,6 +199,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -234,16 +259,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -370,119 +399,119 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.87"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="0" t="s">
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="C3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="C4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="C5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="0" t="n">
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="0" t="n">
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -490,7 +519,7 @@
       <c r="A9" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="0" t="n">
@@ -501,30 +530,30 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="0" t="s">
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="0" t="s">
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -532,108 +561,153 @@
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="0" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="0" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="0" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="0" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="0" t="s">
+      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="0" t="s">
+      <c r="B18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="0" t="s">
+      <c r="B19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>46</v>
       </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
